--- a/출력결과/2849-2018-019318_25696174641_RIS_등기부.xlsx
+++ b/출력결과/2849-2018-019318_25696174641_RIS_등기부.xlsx
@@ -95,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,6 +107,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -475,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -529,7 +531,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>(추출 실패)</t>
+          <t>2849-2018-019318</t>
         </is>
       </c>
     </row>
@@ -541,7 +543,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>(추출 실패)</t>
+          <t>경기도파주시파평면마산리113-2</t>
         </is>
       </c>
     </row>
@@ -553,7 +555,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>(추출 실패)</t>
+          <t>토지</t>
         </is>
       </c>
     </row>
@@ -570,22 +572,745 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>[【표제부】 — 데이터 없음]</t>
-        </is>
-      </c>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>【표제부】</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>고유번호2849-2018-019318</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2023년02월20일</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시파평면</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>마산리113-2</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>1소유권이전1997년09월11일 | 199748428 | 소유자이은470810-※※※※※※※</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>(A 1)Al 42567. 매매경기도 BPA)중부면오전리220-1</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>분할로인하여순위제1번등기를경기도</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>파주시파평면마산리113-1에서이기</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>제99956호</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>2소유권이전2018년12월24일 | 2018년07월24일공유자</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>제107414호매매지분2분의1</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>강성원620910-*※*※※※※※※</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시문산읍사임당로65-30</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>지분2분의1</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>@ | ee 7](0728-*%※%※%※※※%※※</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시문산읍사임당로65-30</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>매매목록제2018-3005호</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>32020년03월04일지분2분의1</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>제18166호</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>기</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>열람일시 : 2026년03월31일17시25분59초</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>7](0728-*※※*※※*※*※※</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>도파주시문산음사임당로65-30</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>2020년07월08일2020년07월02일</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>제56432호해제</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>6임의경매개시결정</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>웨</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>2025141129172 | 202541128172 | 채권자 _ 북파주농업협동조힙15636-0000297</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>제6029598호 _ | 의정부지방법원경기도파주시문산읍</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>고양지원의</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>임의경매개시결</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>정(2025타경647</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>&lt; 전33 | HS</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>유 AVA</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>열람일시 : 2026403831417시25분59초</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>지]경기도파주시파평면마산리113-2</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>eves]5199 | a4 en</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>권리자및기타사항</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>분할로인하여순위제1번부터2번까지능기를</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시파평면마산리113-1에서이기</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>AF 20184118274</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n"/>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>제99956호</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>3 aS ㅋ 42월34웅22249</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="8" t="n"/>
+      <c r="F55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>ANOS = 설정계약</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>그 TCI</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>41번근저당권설정등 | 2018년12월24일 | 20184128249</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>기말소제107416호해지</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>52번지상권설정능기 | 32018년12월24일 | 20184128249</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>말소제107417호해지</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="8" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>6 {abt ㅋ 42월34웅22494 ′</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>제3674348호살종계약범 - 위 - 도자곤부</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n"/>
+      <c r="C63" s="8" t="n"/>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="8" t="n"/>
+      <c r="F63" s="8" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>73번근저당권설정능 ，2024년02월14일 | 20244281448</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="8" t="n"/>
+      <c r="E64" s="8" t="n"/>
+      <c r="F64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>기말소제10276호해지</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n"/>
+      <c r="C65" s="8" t="n"/>
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="8" t="n"/>
+      <c r="F65" s="8" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>86번지상권설정능기 | 2024428149 | 20244281448</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="8" t="n"/>
+      <c r="F66" s="8" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>열람일시 : 2026년03월31일17시25분59초</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n"/>
+      <c r="C67" s="8" t="n"/>
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="8" t="n"/>
+      <c r="F67" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="64">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A57:F57"/>
     <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="C6:H6"/>
-    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A60:F60"/>
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -597,7 +1322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -616,15 +1341,413 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>[【갑구】 — 데이터 없음]</t>
-        </is>
-      </c>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>【갑구】</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>말소제10277호해지</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>9근저당권설정2024년02월14일 ， 2024년02월14일채권최고액금221,000,000원</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>제10278호설정계약 AEX 이순옥</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시문산읍사임당로65-30</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>근저당권자북파주농업협동조합</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>115636-0000297</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시문산읍문향로75</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>(파평지점)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>공동담보목록제2024-225호</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>10근저당권설정2024년02월14일2024년02월14일채권최고액금130,000,000원</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>제10279호설정계약 AEX 이순옥</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시문산읍사임당로65-30</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>근저당권자북파주농업협동조합</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>115636-0000297</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시문산읍문향로75</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>(파평지점)</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>〈_꽤 - ㅠ 7} oS Al]2024-2268.</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>11지상권설정2024톨떨촬욜일20241큭′휠_모끓끝</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>제10280호 ㅋ Ag 73 APE</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>2024144849)</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>제29644호</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>열람일시 : 2026년03월31일17시25분59초</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>2024년04월04일</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>설정계약</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>채권최고액금360,000,000원</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>채무자강성원</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시문산읍사임당로65-30</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>서울특별시마포구마포대로4라길30,106농</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>802호(마포농 , 마포쌍용황금아파트)</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>공동담보목록제2024-558호</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="32">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="B1:F1"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -675,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -696,15 +1819,3921 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>[【공동담보목록】 — 데이터 없음]</t>
-        </is>
-      </c>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>【공동담보목록】</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>ESS | 2023-233</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>일련번호부동산에관한권리의표시관할능기소명</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>4202414281424</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>체30833호제10276호</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>분할로 - 완 ㅎ 해지</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>2근3 宰 20e 2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>제36833초제10276호</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>해지</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>320241424144</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>A 10276</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>열람일시 : 2026403831417시25분59초</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>기타사항</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>이0</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>일련번호부동산에</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>한권리의</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>시</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>생성원인변경 / 소멸</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>파주능분활로 - 완하여 | 해지</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>제10276호</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>해지</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>2023년07월25일</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>제53675호</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>HAE 인하여</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>62024년02월14일</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>제10276호</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>해지</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>우2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>제10276호</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>해지</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>목록번호 」 2024-225쿨</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>제10278호</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>설정계약으로</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>파주시파평면마산리</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>113-2고양지원제10278호</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>설정계약으로</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>파주시파평면마산리 | 의정부지2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>고양지원제10278호</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>파주능기설정계약으로</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>열람일시 : 2026년03월31일17시25분59초</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>기타사항</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>일련번호부동산에관한권리의표시관할등기소명호</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>생성원인변경 / 소멸</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>4 | [eA]경기도파주시파평면마산리 | 의정부지방법원 _ | 92024142914)</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n"/>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>산44-16고양지원제10278호</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>파주등기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="8" t="n"/>
+      <c r="F55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>5 | [토지]경기도파주시파평면마산리 | 의정부지방법원2024142914)</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>113-4고양지원제10278호</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>파주등기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시파평면마산리 | 의정부지방법원20241429149)</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="8" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>115-21고양지원제10278호</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>설정계약으로</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n"/>
+      <c r="C63" s="8" t="n"/>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="8" t="n"/>
+      <c r="F63" s="8" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="8" t="n"/>
+      <c r="E64" s="8" t="n"/>
+      <c r="F64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시파평면마산리20241429149)</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n"/>
+      <c r="C65" s="8" t="n"/>
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="8" t="n"/>
+      <c r="F65" s="8" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>115-22 Al]102788.</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="8" t="n"/>
+      <c r="F66" s="8" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Or 설정계약으로</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n"/>
+      <c r="C67" s="8" t="n"/>
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="8" t="n"/>
+      <c r="F67" s="8" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>6220인하여</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="8" t="n"/>
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="8" t="n"/>
+      <c r="F68" s="8" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시파평면마산리 | 의정부지20241429149)</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n"/>
+      <c r="C69" s="8" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="8" t="n"/>
+      <c r="F69" s="8" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>115-24고양지원제10278호</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n"/>
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="8" t="n"/>
+      <c r="E70" s="8" t="n"/>
+      <c r="F70" s="8" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>파주등기설정계약으로</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n"/>
+      <c r="C71" s="8" t="n"/>
+      <c r="D71" s="8" t="n"/>
+      <c r="E71" s="8" t="n"/>
+      <c r="F71" s="8" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="8" t="n"/>
+      <c r="D72" s="8" t="n"/>
+      <c r="E72" s="8" t="n"/>
+      <c r="F72" s="8" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시파평면마산리 | 의정부지방법원2024142914)</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n"/>
+      <c r="C73" s="8" t="n"/>
+      <c r="D73" s="8" t="n"/>
+      <c r="E73" s="8" t="n"/>
+      <c r="F73" s="8" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>115-20고양지원제10278호</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n"/>
+      <c r="C74" s="8" t="n"/>
+      <c r="D74" s="8" t="n"/>
+      <c r="E74" s="8" t="n"/>
+      <c r="F74" s="8" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>파주등기설정계약으로</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n"/>
+      <c r="C75" s="8" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="8" t="n"/>
+      <c r="F75" s="8" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="8" t="n"/>
+      <c r="D76" s="8" t="n"/>
+      <c r="E76" s="8" t="n"/>
+      <c r="F76" s="8" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>10 | [토지]경기도파주시파평면마산리 | 의정부지방법원2024142914)</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n"/>
+      <c r="C77" s="8" t="n"/>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="8" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>115-23고양지원제10278호</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n"/>
+      <c r="C78" s="8" t="n"/>
+      <c r="D78" s="8" t="n"/>
+      <c r="E78" s="8" t="n"/>
+      <c r="F78" s="8" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>파주등기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n"/>
+      <c r="C79" s="8" t="n"/>
+      <c r="D79" s="8" t="n"/>
+      <c r="E79" s="8" t="n"/>
+      <c r="F79" s="8" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="8" t="n"/>
+      <c r="D80" s="8" t="n"/>
+      <c r="E80" s="8" t="n"/>
+      <c r="F80" s="8" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>11 。 | | [토지]경기도파주시파평면마산리 | 의정부지방법원20241429149)</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n"/>
+      <c r="C81" s="8" t="n"/>
+      <c r="D81" s="8" t="n"/>
+      <c r="E81" s="8" t="n"/>
+      <c r="F81" s="8" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>108-3고양지원제10278호</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n"/>
+      <c r="C82" s="8" t="n"/>
+      <c r="D82" s="8" t="n"/>
+      <c r="E82" s="8" t="n"/>
+      <c r="F82" s="8" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>파주등기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n"/>
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="8" t="n"/>
+      <c r="F83" s="8" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="n"/>
+      <c r="C84" s="8" t="n"/>
+      <c r="D84" s="8" t="n"/>
+      <c r="E84" s="8" t="n"/>
+      <c r="F84" s="8" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>열람일시 : 2026년03월31일17시25분59초</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="8" t="n"/>
+      <c r="F85" s="8" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>한권리의</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="n"/>
+      <c r="C86" s="8" t="n"/>
+      <c r="D86" s="8" t="n"/>
+      <c r="E86" s="8" t="n"/>
+      <c r="F86" s="8" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>시</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n"/>
+      <c r="C87" s="8" t="n"/>
+      <c r="D87" s="8" t="n"/>
+      <c r="E87" s="8" t="n"/>
+      <c r="F87" s="8" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>구스기소</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="n"/>
+      <c r="C88" s="8" t="n"/>
+      <c r="D88" s="8" t="n"/>
+      <c r="E88" s="8" t="n"/>
+      <c r="F88" s="8" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>생성원인</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n"/>
+      <c r="C89" s="8" t="n"/>
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="8" t="n"/>
+      <c r="F89" s="8" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>12[토지]경기도파주시파평면마산리</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="n"/>
+      <c r="C90" s="8" t="n"/>
+      <c r="D90" s="8" t="n"/>
+      <c r="E90" s="8" t="n"/>
+      <c r="F90" s="8" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>브</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n"/>
+      <c r="C91" s="8" t="n"/>
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="8" t="n"/>
+      <c r="F91" s="8" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>의정부지방범원</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="n"/>
+      <c r="C92" s="8" t="n"/>
+      <c r="D92" s="8" t="n"/>
+      <c r="E92" s="8" t="n"/>
+      <c r="F92" s="8" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>고양지욱</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="8" t="n"/>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="8" t="n"/>
+      <c r="F93" s="8" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>파주등기소</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="n"/>
+      <c r="C94" s="8" t="n"/>
+      <c r="D94" s="8" t="n"/>
+      <c r="E94" s="8" t="n"/>
+      <c r="F94" s="8" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="n"/>
+      <c r="C95" s="8" t="n"/>
+      <c r="D95" s="8" t="n"/>
+      <c r="E95" s="8" t="n"/>
+      <c r="F95" s="8" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>제10278호</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="n"/>
+      <c r="C96" s="8" t="n"/>
+      <c r="D96" s="8" t="n"/>
+      <c r="E96" s="8" t="n"/>
+      <c r="F96" s="8" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>설정계약으로</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="n"/>
+      <c r="C97" s="8" t="n"/>
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="8" t="n"/>
+      <c r="F97" s="8" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="n"/>
+      <c r="C98" s="8" t="n"/>
+      <c r="D98" s="8" t="n"/>
+      <c r="E98" s="8" t="n"/>
+      <c r="F98" s="8" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>13[토지]경기도파주시파평면마산리</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="n"/>
+      <c r="C99" s="8" t="n"/>
+      <c r="D99" s="8" t="n"/>
+      <c r="E99" s="8" t="n"/>
+      <c r="F99" s="8" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>파주시파평면마산리</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="8" t="n"/>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="8" t="n"/>
+      <c r="F100" s="8" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>의정부지방</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="n"/>
+      <c r="C101" s="8" t="n"/>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="8" t="n"/>
+      <c r="F101" s="8" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>고양지원</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="n"/>
+      <c r="C102" s="8" t="n"/>
+      <c r="D102" s="8" t="n"/>
+      <c r="E102" s="8" t="n"/>
+      <c r="F102" s="8" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>파주능기소</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="8" t="n"/>
+      <c r="D103" s="8" t="n"/>
+      <c r="E103" s="8" t="n"/>
+      <c r="F103" s="8" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="8" t="n"/>
+      <c r="D104" s="8" t="n"/>
+      <c r="E104" s="8" t="n"/>
+      <c r="F104" s="8" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>제10278호</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="n"/>
+      <c r="C105" s="8" t="n"/>
+      <c r="D105" s="8" t="n"/>
+      <c r="E105" s="8" t="n"/>
+      <c r="F105" s="8" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>설정계약으로</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="n"/>
+      <c r="C106" s="8" t="n"/>
+      <c r="D106" s="8" t="n"/>
+      <c r="E106" s="8" t="n"/>
+      <c r="F106" s="8" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="n"/>
+      <c r="C107" s="8" t="n"/>
+      <c r="D107" s="8" t="n"/>
+      <c r="E107" s="8" t="n"/>
+      <c r="F107" s="8" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="n"/>
+      <c r="C108" s="8" t="n"/>
+      <c r="D108" s="8" t="n"/>
+      <c r="E108" s="8" t="n"/>
+      <c r="F108" s="8" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>제10278호</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="n"/>
+      <c r="C109" s="8" t="n"/>
+      <c r="D109" s="8" t="n"/>
+      <c r="E109" s="8" t="n"/>
+      <c r="F109" s="8" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>설정계약으로</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="n"/>
+      <c r="C110" s="8" t="n"/>
+      <c r="D110" s="8" t="n"/>
+      <c r="E110" s="8" t="n"/>
+      <c r="F110" s="8" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="8" t="n"/>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="8" t="n"/>
+      <c r="F111" s="8" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>훠기타사항</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="n"/>
+      <c r="C112" s="8" t="n"/>
+      <c r="D112" s="8" t="n"/>
+      <c r="E112" s="8" t="n"/>
+      <c r="F112" s="8" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>일련번호부동산에관한권리의표처 SAW Sse</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="n"/>
+      <c r="C113" s="8" t="n"/>
+      <c r="D113" s="8" t="n"/>
+      <c r="E113" s="8" t="n"/>
+      <c r="F113" s="8" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>근 UW “Tou L ‘O 0 We</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="n"/>
+      <c r="C114" s="8" t="n"/>
+      <c r="D114" s="8" t="n"/>
+      <c r="E114" s="8" t="n"/>
+      <c r="F114" s="8" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>래 CD 생성원인</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="n"/>
+      <c r="C115" s="8" t="n"/>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="8" t="n"/>
+      <c r="F115" s="8" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>1 。 | (24)경기도파주시파평면마산리 | 의정부지방법원 _ | 62034년02월14일</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="n"/>
+      <c r="C116" s="8" t="n"/>
+      <c r="D116" s="8" t="n"/>
+      <c r="E116" s="8" t="n"/>
+      <c r="F116" s="8" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>113-38고양지원제10279호</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="n"/>
+      <c r="C117" s="8" t="n"/>
+      <c r="D117" s="8" t="n"/>
+      <c r="E117" s="8" t="n"/>
+      <c r="F117" s="8" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>파주등기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="n"/>
+      <c r="C118" s="8" t="n"/>
+      <c r="D118" s="8" t="n"/>
+      <c r="E118" s="8" t="n"/>
+      <c r="F118" s="8" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="n"/>
+      <c r="C119" s="8" t="n"/>
+      <c r="D119" s="8" t="n"/>
+      <c r="E119" s="8" t="n"/>
+      <c r="F119" s="8" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>2 | [토지]경기도파주시파평면마산리 | 의정부지방법원102024년02월14일</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="n"/>
+      <c r="C120" s="8" t="n"/>
+      <c r="D120" s="8" t="n"/>
+      <c r="E120" s="8" t="n"/>
+      <c r="F120" s="8" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>113-2고양지원제10279호</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="n"/>
+      <c r="C121" s="8" t="n"/>
+      <c r="D121" s="8" t="n"/>
+      <c r="E121" s="8" t="n"/>
+      <c r="F121" s="8" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>파주등기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="n"/>
+      <c r="C122" s="8" t="n"/>
+      <c r="D122" s="8" t="n"/>
+      <c r="E122" s="8" t="n"/>
+      <c r="F122" s="8" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="n"/>
+      <c r="C123" s="8" t="n"/>
+      <c r="D123" s="8" t="n"/>
+      <c r="E123" s="8" t="n"/>
+      <c r="F123" s="8" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>3 | [24]경기도파주시파평면마산리 | geal 102034년02월14일</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="n"/>
+      <c r="C124" s="8" t="n"/>
+      <c r="D124" s="8" t="n"/>
+      <c r="E124" s="8" t="n"/>
+      <c r="F124" s="8" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>113-1고양지원제10279호</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="n"/>
+      <c r="C125" s="8" t="n"/>
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="8" t="n"/>
+      <c r="F125" s="8" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>파주등기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="n"/>
+      <c r="C126" s="8" t="n"/>
+      <c r="D126" s="8" t="n"/>
+      <c r="E126" s="8" t="n"/>
+      <c r="F126" s="8" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="n"/>
+      <c r="C127" s="8" t="n"/>
+      <c r="D127" s="8" t="n"/>
+      <c r="E127" s="8" t="n"/>
+      <c r="F127" s="8" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>4 | [24]경기도파주시파평면마산리 | 의정부지방법원102034년02월14일</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="n"/>
+      <c r="C128" s="8" t="n"/>
+      <c r="D128" s="8" t="n"/>
+      <c r="E128" s="8" t="n"/>
+      <c r="F128" s="8" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>산44-16고양지원제10279호</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="n"/>
+      <c r="C129" s="8" t="n"/>
+      <c r="D129" s="8" t="n"/>
+      <c r="E129" s="8" t="n"/>
+      <c r="F129" s="8" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>파주등기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="n"/>
+      <c r="C130" s="8" t="n"/>
+      <c r="D130" s="8" t="n"/>
+      <c r="E130" s="8" t="n"/>
+      <c r="F130" s="8" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>열람일시 : 2026년03월31일17시25분59초</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="n"/>
+      <c r="C131" s="8" t="n"/>
+      <c r="D131" s="8" t="n"/>
+      <c r="E131" s="8" t="n"/>
+      <c r="F131" s="8" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>기타사항</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="n"/>
+      <c r="C132" s="8" t="n"/>
+      <c r="D132" s="8" t="n"/>
+      <c r="E132" s="8" t="n"/>
+      <c r="F132" s="8" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>생성원인변경 / 소멸</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="n"/>
+      <c r="C133" s="8" t="n"/>
+      <c r="D133" s="8" t="n"/>
+      <c r="E133" s="8" t="n"/>
+      <c r="F133" s="8" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="n"/>
+      <c r="C134" s="8" t="n"/>
+      <c r="D134" s="8" t="n"/>
+      <c r="E134" s="8" t="n"/>
+      <c r="F134" s="8" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>9[토지]경기도파주시파평면마산리 | ， 의정부지방법원2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="n"/>
+      <c r="C135" s="8" t="n"/>
+      <c r="D135" s="8" t="n"/>
+      <c r="E135" s="8" t="n"/>
+      <c r="F135" s="8" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>113-4고양지원제10279호</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="n"/>
+      <c r="C136" s="8" t="n"/>
+      <c r="D136" s="8" t="n"/>
+      <c r="E136" s="8" t="n"/>
+      <c r="F136" s="8" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>파주능기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="n"/>
+      <c r="C137" s="8" t="n"/>
+      <c r="D137" s="8" t="n"/>
+      <c r="E137" s="8" t="n"/>
+      <c r="F137" s="8" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="n"/>
+      <c r="C138" s="8" t="n"/>
+      <c r="D138" s="8" t="n"/>
+      <c r="E138" s="8" t="n"/>
+      <c r="F138" s="8" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>파주시파평면마산리 ， 의정부지방법원2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="n"/>
+      <c r="C139" s="8" t="n"/>
+      <c r="D139" s="8" t="n"/>
+      <c r="E139" s="8" t="n"/>
+      <c r="F139" s="8" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>고양지원제10279호</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="n"/>
+      <c r="C140" s="8" t="n"/>
+      <c r="D140" s="8" t="n"/>
+      <c r="E140" s="8" t="n"/>
+      <c r="F140" s="8" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>파주능기설정계약으로</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="n"/>
+      <c r="C141" s="8" t="n"/>
+      <c r="D141" s="8" t="n"/>
+      <c r="E141" s="8" t="n"/>
+      <c r="F141" s="8" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="n"/>
+      <c r="C142" s="8" t="n"/>
+      <c r="D142" s="8" t="n"/>
+      <c r="E142" s="8" t="n"/>
+      <c r="F142" s="8" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>7 | [EAI]경기도파주시파평면마산리 | 의정부지방범원2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="n"/>
+      <c r="C143" s="8" t="n"/>
+      <c r="D143" s="8" t="n"/>
+      <c r="E143" s="8" t="n"/>
+      <c r="F143" s="8" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>115-22고양지원제10279호</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="n"/>
+      <c r="C144" s="8" t="n"/>
+      <c r="D144" s="8" t="n"/>
+      <c r="E144" s="8" t="n"/>
+      <c r="F144" s="8" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>파주등기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="n"/>
+      <c r="C145" s="8" t="n"/>
+      <c r="D145" s="8" t="n"/>
+      <c r="E145" s="8" t="n"/>
+      <c r="F145" s="8" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="n"/>
+      <c r="C146" s="8" t="n"/>
+      <c r="D146" s="8" t="n"/>
+      <c r="E146" s="8" t="n"/>
+      <c r="F146" s="8" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>8 . | [토지]경기도과주시파평면 abe 의정부치망밖원2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="n"/>
+      <c r="C147" s="8" t="n"/>
+      <c r="D147" s="8" t="n"/>
+      <c r="E147" s="8" t="n"/>
+      <c r="F147" s="8" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>115-24고양착원제10279호</t>
+        </is>
+      </c>
+      <c r="B148" s="8" t="n"/>
+      <c r="C148" s="8" t="n"/>
+      <c r="D148" s="8" t="n"/>
+      <c r="E148" s="8" t="n"/>
+      <c r="F148" s="8" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>classed 설정계약으로</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="n"/>
+      <c r="C149" s="8" t="n"/>
+      <c r="D149" s="8" t="n"/>
+      <c r="E149" s="8" t="n"/>
+      <c r="F149" s="8" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B150" s="8" t="n"/>
+      <c r="C150" s="8" t="n"/>
+      <c r="D150" s="8" t="n"/>
+      <c r="E150" s="8" t="n"/>
+      <c r="F150" s="8" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>9 | [토지]경기도파주시파평면마산리 | 의정부지방범원2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B151" s="8" t="n"/>
+      <c r="C151" s="8" t="n"/>
+      <c r="D151" s="8" t="n"/>
+      <c r="E151" s="8" t="n"/>
+      <c r="F151" s="8" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>115-20고양지원제10279호</t>
+        </is>
+      </c>
+      <c r="B152" s="8" t="n"/>
+      <c r="C152" s="8" t="n"/>
+      <c r="D152" s="8" t="n"/>
+      <c r="E152" s="8" t="n"/>
+      <c r="F152" s="8" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>파주등기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="n"/>
+      <c r="C153" s="8" t="n"/>
+      <c r="D153" s="8" t="n"/>
+      <c r="E153" s="8" t="n"/>
+      <c r="F153" s="8" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="n"/>
+      <c r="C154" s="8" t="n"/>
+      <c r="D154" s="8" t="n"/>
+      <c r="E154" s="8" t="n"/>
+      <c r="F154" s="8" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>10 。 | [AI]경기도파주시파평먼마산리 | 의정부지방범원2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="n"/>
+      <c r="C155" s="8" t="n"/>
+      <c r="D155" s="8" t="n"/>
+      <c r="E155" s="8" t="n"/>
+      <c r="F155" s="8" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>115-23고양지원제10279호</t>
+        </is>
+      </c>
+      <c r="B156" s="8" t="n"/>
+      <c r="C156" s="8" t="n"/>
+      <c r="D156" s="8" t="n"/>
+      <c r="E156" s="8" t="n"/>
+      <c r="F156" s="8" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>파주등기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="n"/>
+      <c r="C157" s="8" t="n"/>
+      <c r="D157" s="8" t="n"/>
+      <c r="E157" s="8" t="n"/>
+      <c r="F157" s="8" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B158" s="8" t="n"/>
+      <c r="C158" s="8" t="n"/>
+      <c r="D158" s="8" t="n"/>
+      <c r="E158" s="8" t="n"/>
+      <c r="F158" s="8" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>11 | (4)경기도파주시파평먼마산리 | 의정부지방범원2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="n"/>
+      <c r="C159" s="8" t="n"/>
+      <c r="D159" s="8" t="n"/>
+      <c r="E159" s="8" t="n"/>
+      <c r="F159" s="8" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t>108-3고양지원제10279호</t>
+        </is>
+      </c>
+      <c r="B160" s="8" t="n"/>
+      <c r="C160" s="8" t="n"/>
+      <c r="D160" s="8" t="n"/>
+      <c r="E160" s="8" t="n"/>
+      <c r="F160" s="8" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t>파주등기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B161" s="8" t="n"/>
+      <c r="C161" s="8" t="n"/>
+      <c r="D161" s="8" t="n"/>
+      <c r="E161" s="8" t="n"/>
+      <c r="F161" s="8" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B162" s="8" t="n"/>
+      <c r="C162" s="8" t="n"/>
+      <c r="D162" s="8" t="n"/>
+      <c r="E162" s="8" t="n"/>
+      <c r="F162" s="8" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t>12 | [토지]경기도파주시파평면마산리 | 의정부지방법원 _ | 22024년02월14일</t>
+        </is>
+      </c>
+      <c r="B163" s="8" t="n"/>
+      <c r="C163" s="8" t="n"/>
+      <c r="D163" s="8" t="n"/>
+      <c r="E163" s="8" t="n"/>
+      <c r="F163" s="8" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t>108-4고양지원제10279호</t>
+        </is>
+      </c>
+      <c r="B164" s="8" t="n"/>
+      <c r="C164" s="8" t="n"/>
+      <c r="D164" s="8" t="n"/>
+      <c r="E164" s="8" t="n"/>
+      <c r="F164" s="8" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>열람일시 : 2026년03월31일17시25분59초</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="n"/>
+      <c r="C165" s="8" t="n"/>
+      <c r="D165" s="8" t="n"/>
+      <c r="E165" s="8" t="n"/>
+      <c r="F165" s="8" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>일련번호부농산에관한권리의표시관할능기소명</t>
+        </is>
+      </c>
+      <c r="B166" s="8" t="n"/>
+      <c r="C166" s="8" t="n"/>
+      <c r="D166" s="8" t="n"/>
+      <c r="E166" s="8" t="n"/>
+      <c r="F166" s="8" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t>생성원인변경 / 소멸</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="n"/>
+      <c r="C167" s="8" t="n"/>
+      <c r="D167" s="8" t="n"/>
+      <c r="E167" s="8" t="n"/>
+      <c r="F167" s="8" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>설정계약으로</t>
+        </is>
+      </c>
+      <c r="B168" s="8" t="n"/>
+      <c r="C168" s="8" t="n"/>
+      <c r="D168" s="8" t="n"/>
+      <c r="E168" s="8" t="n"/>
+      <c r="F168" s="8" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B169" s="8" t="n"/>
+      <c r="C169" s="8" t="n"/>
+      <c r="D169" s="8" t="n"/>
+      <c r="E169" s="8" t="n"/>
+      <c r="F169" s="8" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t>109-3고양지원제10279호</t>
+        </is>
+      </c>
+      <c r="B170" s="8" t="n"/>
+      <c r="C170" s="8" t="n"/>
+      <c r="D170" s="8" t="n"/>
+      <c r="E170" s="8" t="n"/>
+      <c r="F170" s="8" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t>파주능기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B171" s="8" t="n"/>
+      <c r="C171" s="8" t="n"/>
+      <c r="D171" s="8" t="n"/>
+      <c r="E171" s="8" t="n"/>
+      <c r="F171" s="8" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B172" s="8" t="n"/>
+      <c r="C172" s="8" t="n"/>
+      <c r="D172" s="8" t="n"/>
+      <c r="E172" s="8" t="n"/>
+      <c r="F172" s="8" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>14[토지]경기도파주시파평면마산리 ， 의정부지방법원2024년02월14일</t>
+        </is>
+      </c>
+      <c r="B173" s="8" t="n"/>
+      <c r="C173" s="8" t="n"/>
+      <c r="D173" s="8" t="n"/>
+      <c r="E173" s="8" t="n"/>
+      <c r="F173" s="8" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t>116-15고양지원제10279호</t>
+        </is>
+      </c>
+      <c r="B174" s="8" t="n"/>
+      <c r="C174" s="8" t="n"/>
+      <c r="D174" s="8" t="n"/>
+      <c r="E174" s="8" t="n"/>
+      <c r="F174" s="8" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
+        <is>
+          <t>파주능기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B175" s="8" t="n"/>
+      <c r="C175" s="8" t="n"/>
+      <c r="D175" s="8" t="n"/>
+      <c r="E175" s="8" t="n"/>
+      <c r="F175" s="8" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B176" s="8" t="n"/>
+      <c r="C176" s="8" t="n"/>
+      <c r="D176" s="8" t="n"/>
+      <c r="E176" s="8" t="n"/>
+      <c r="F176" s="8" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t>ESS | 2024-558</t>
+        </is>
+      </c>
+      <c r="B177" s="8" t="n"/>
+      <c r="C177" s="8" t="n"/>
+      <c r="D177" s="8" t="n"/>
+      <c r="E177" s="8" t="n"/>
+      <c r="F177" s="8" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="7" t="inlineStr">
+        <is>
+          <t>113-1원제29644호</t>
+        </is>
+      </c>
+      <c r="B178" s="8" t="n"/>
+      <c r="C178" s="8" t="n"/>
+      <c r="D178" s="8" t="n"/>
+      <c r="E178" s="8" t="n"/>
+      <c r="F178" s="8" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>설정계약으로</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="n"/>
+      <c r="C179" s="8" t="n"/>
+      <c r="D179" s="8" t="n"/>
+      <c r="E179" s="8" t="n"/>
+      <c r="F179" s="8" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B180" s="8" t="n"/>
+      <c r="C180" s="8" t="n"/>
+      <c r="D180" s="8" t="n"/>
+      <c r="E180" s="8" t="n"/>
+      <c r="F180" s="8" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>113-2고양지원제29644호</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="n"/>
+      <c r="C181" s="8" t="n"/>
+      <c r="D181" s="8" t="n"/>
+      <c r="E181" s="8" t="n"/>
+      <c r="F181" s="8" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>파주능기설정계약으로</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="n"/>
+      <c r="C182" s="8" t="n"/>
+      <c r="D182" s="8" t="n"/>
+      <c r="E182" s="8" t="n"/>
+      <c r="F182" s="8" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B183" s="8" t="n"/>
+      <c r="C183" s="8" t="n"/>
+      <c r="D183" s="8" t="n"/>
+      <c r="E183" s="8" t="n"/>
+      <c r="F183" s="8" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="7" t="inlineStr">
+        <is>
+          <t>113-3고양지원제29644호</t>
+        </is>
+      </c>
+      <c r="B184" s="8" t="n"/>
+      <c r="C184" s="8" t="n"/>
+      <c r="D184" s="8" t="n"/>
+      <c r="E184" s="8" t="n"/>
+      <c r="F184" s="8" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>파주능기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B185" s="8" t="n"/>
+      <c r="C185" s="8" t="n"/>
+      <c r="D185" s="8" t="n"/>
+      <c r="E185" s="8" t="n"/>
+      <c r="F185" s="8" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B186" s="8" t="n"/>
+      <c r="C186" s="8" t="n"/>
+      <c r="D186" s="8" t="n"/>
+      <c r="E186" s="8" t="n"/>
+      <c r="F186" s="8" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>113-4고양지원제29644호</t>
+        </is>
+      </c>
+      <c r="B187" s="8" t="n"/>
+      <c r="C187" s="8" t="n"/>
+      <c r="D187" s="8" t="n"/>
+      <c r="E187" s="8" t="n"/>
+      <c r="F187" s="8" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="7" t="inlineStr">
+        <is>
+          <t>파주능기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B188" s="8" t="n"/>
+      <c r="C188" s="8" t="n"/>
+      <c r="D188" s="8" t="n"/>
+      <c r="E188" s="8" t="n"/>
+      <c r="F188" s="8" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B189" s="8" t="n"/>
+      <c r="C189" s="8" t="n"/>
+      <c r="D189" s="8" t="n"/>
+      <c r="E189" s="8" t="n"/>
+      <c r="F189" s="8" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="7" t="inlineStr">
+        <is>
+          <t>열람일시 : 2026년03월31일17시25분59초</t>
+        </is>
+      </c>
+      <c r="B190" s="8" t="n"/>
+      <c r="C190" s="8" t="n"/>
+      <c r="D190" s="8" t="n"/>
+      <c r="E190" s="8" t="n"/>
+      <c r="F190" s="8" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="7" t="inlineStr">
+        <is>
+          <t>기타사항</t>
+        </is>
+      </c>
+      <c r="B191" s="8" t="n"/>
+      <c r="C191" s="8" t="n"/>
+      <c r="D191" s="8" t="n"/>
+      <c r="E191" s="8" t="n"/>
+      <c r="F191" s="8" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="7" t="inlineStr">
+        <is>
+          <t>생성원인변</t>
+        </is>
+      </c>
+      <c r="B192" s="8" t="n"/>
+      <c r="C192" s="8" t="n"/>
+      <c r="D192" s="8" t="n"/>
+      <c r="E192" s="8" t="n"/>
+      <c r="F192" s="8" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>9[토지]경기도파주시파평면마산리 ， 의정부지2024년04월04일</t>
+        </is>
+      </c>
+      <c r="B193" s="8" t="n"/>
+      <c r="C193" s="8" t="n"/>
+      <c r="D193" s="8" t="n"/>
+      <c r="E193" s="8" t="n"/>
+      <c r="F193" s="8" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t>산44-16 ALA]¢ 제29644호</t>
+        </is>
+      </c>
+      <c r="B194" s="8" t="n"/>
+      <c r="C194" s="8" t="n"/>
+      <c r="D194" s="8" t="n"/>
+      <c r="E194" s="8" t="n"/>
+      <c r="F194" s="8" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t>파주등설정계약으로</t>
+        </is>
+      </c>
+      <c r="B195" s="8" t="n"/>
+      <c r="C195" s="8" t="n"/>
+      <c r="D195" s="8" t="n"/>
+      <c r="E195" s="8" t="n"/>
+      <c r="F195" s="8" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B196" s="8" t="n"/>
+      <c r="C196" s="8" t="n"/>
+      <c r="D196" s="8" t="n"/>
+      <c r="E196" s="8" t="n"/>
+      <c r="F196" s="8" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t>6[토지]경기도파주시파평면마산리 ， 의정부지2024년04월04일</t>
+        </is>
+      </c>
+      <c r="B197" s="8" t="n"/>
+      <c r="C197" s="8" t="n"/>
+      <c r="D197" s="8" t="n"/>
+      <c r="E197" s="8" t="n"/>
+      <c r="F197" s="8" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>115-20고양지원제29644호</t>
+        </is>
+      </c>
+      <c r="B198" s="8" t="n"/>
+      <c r="C198" s="8" t="n"/>
+      <c r="D198" s="8" t="n"/>
+      <c r="E198" s="8" t="n"/>
+      <c r="F198" s="8" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t>파주능기설정계약으로</t>
+        </is>
+      </c>
+      <c r="B199" s="8" t="n"/>
+      <c r="C199" s="8" t="n"/>
+      <c r="D199" s="8" t="n"/>
+      <c r="E199" s="8" t="n"/>
+      <c r="F199" s="8" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B200" s="8" t="n"/>
+      <c r="C200" s="8" t="n"/>
+      <c r="D200" s="8" t="n"/>
+      <c r="E200" s="8" t="n"/>
+      <c r="F200" s="8" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시파평면마산리</t>
+        </is>
+      </c>
+      <c r="B201" s="8" t="n"/>
+      <c r="C201" s="8" t="n"/>
+      <c r="D201" s="8" t="n"/>
+      <c r="E201" s="8" t="n"/>
+      <c r="F201" s="8" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시파평면마산리</t>
+        </is>
+      </c>
+      <c r="B202" s="8" t="n"/>
+      <c r="C202" s="8" t="n"/>
+      <c r="D202" s="8" t="n"/>
+      <c r="E202" s="8" t="n"/>
+      <c r="F202" s="8" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시파평면마산리</t>
+        </is>
+      </c>
+      <c r="B203" s="8" t="n"/>
+      <c r="C203" s="8" t="n"/>
+      <c r="D203" s="8" t="n"/>
+      <c r="E203" s="8" t="n"/>
+      <c r="F203" s="8" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시파평면마산리</t>
+        </is>
+      </c>
+      <c r="B204" s="8" t="n"/>
+      <c r="C204" s="8" t="n"/>
+      <c r="D204" s="8" t="n"/>
+      <c r="E204" s="8" t="n"/>
+      <c r="F204" s="8" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="7" t="inlineStr">
+        <is>
+          <t>의정부지방법</t>
+        </is>
+      </c>
+      <c r="B205" s="8" t="n"/>
+      <c r="C205" s="8" t="n"/>
+      <c r="D205" s="8" t="n"/>
+      <c r="E205" s="8" t="n"/>
+      <c r="F205" s="8" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t>고양지원</t>
+        </is>
+      </c>
+      <c r="B206" s="8" t="n"/>
+      <c r="C206" s="8" t="n"/>
+      <c r="D206" s="8" t="n"/>
+      <c r="E206" s="8" t="n"/>
+      <c r="F206" s="8" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="7" t="inlineStr">
+        <is>
+          <t>의정부지</t>
+        </is>
+      </c>
+      <c r="B207" s="8" t="n"/>
+      <c r="C207" s="8" t="n"/>
+      <c r="D207" s="8" t="n"/>
+      <c r="E207" s="8" t="n"/>
+      <c r="F207" s="8" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="7" t="inlineStr">
+        <is>
+          <t>고양지원</t>
+        </is>
+      </c>
+      <c r="B208" s="8" t="n"/>
+      <c r="C208" s="8" t="n"/>
+      <c r="D208" s="8" t="n"/>
+      <c r="E208" s="8" t="n"/>
+      <c r="F208" s="8" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="7" t="inlineStr">
+        <is>
+          <t>파주능기</t>
+        </is>
+      </c>
+      <c r="B209" s="8" t="n"/>
+      <c r="C209" s="8" t="n"/>
+      <c r="D209" s="8" t="n"/>
+      <c r="E209" s="8" t="n"/>
+      <c r="F209" s="8" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="7" t="inlineStr">
+        <is>
+          <t>의정부지방법</t>
+        </is>
+      </c>
+      <c r="B210" s="8" t="n"/>
+      <c r="C210" s="8" t="n"/>
+      <c r="D210" s="8" t="n"/>
+      <c r="E210" s="8" t="n"/>
+      <c r="F210" s="8" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="7" t="inlineStr">
+        <is>
+          <t>고양지원</t>
+        </is>
+      </c>
+      <c r="B211" s="8" t="n"/>
+      <c r="C211" s="8" t="n"/>
+      <c r="D211" s="8" t="n"/>
+      <c r="E211" s="8" t="n"/>
+      <c r="F211" s="8" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="7" t="inlineStr">
+        <is>
+          <t>파주등기</t>
+        </is>
+      </c>
+      <c r="B212" s="8" t="n"/>
+      <c r="C212" s="8" t="n"/>
+      <c r="D212" s="8" t="n"/>
+      <c r="E212" s="8" t="n"/>
+      <c r="F212" s="8" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="7" t="inlineStr">
+        <is>
+          <t>2024년04월04일</t>
+        </is>
+      </c>
+      <c r="B213" s="8" t="n"/>
+      <c r="C213" s="8" t="n"/>
+      <c r="D213" s="8" t="n"/>
+      <c r="E213" s="8" t="n"/>
+      <c r="F213" s="8" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t>제29644호</t>
+        </is>
+      </c>
+      <c r="B214" s="8" t="n"/>
+      <c r="C214" s="8" t="n"/>
+      <c r="D214" s="8" t="n"/>
+      <c r="E214" s="8" t="n"/>
+      <c r="F214" s="8" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="7" t="inlineStr">
+        <is>
+          <t>설정계약으로</t>
+        </is>
+      </c>
+      <c r="B215" s="8" t="n"/>
+      <c r="C215" s="8" t="n"/>
+      <c r="D215" s="8" t="n"/>
+      <c r="E215" s="8" t="n"/>
+      <c r="F215" s="8" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B216" s="8" t="n"/>
+      <c r="C216" s="8" t="n"/>
+      <c r="D216" s="8" t="n"/>
+      <c r="E216" s="8" t="n"/>
+      <c r="F216" s="8" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="7" t="inlineStr">
+        <is>
+          <t>2024년04월04일</t>
+        </is>
+      </c>
+      <c r="B217" s="8" t="n"/>
+      <c r="C217" s="8" t="n"/>
+      <c r="D217" s="8" t="n"/>
+      <c r="E217" s="8" t="n"/>
+      <c r="F217" s="8" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="7" t="inlineStr">
+        <is>
+          <t>제29644호</t>
+        </is>
+      </c>
+      <c r="B218" s="8" t="n"/>
+      <c r="C218" s="8" t="n"/>
+      <c r="D218" s="8" t="n"/>
+      <c r="E218" s="8" t="n"/>
+      <c r="F218" s="8" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="7" t="inlineStr">
+        <is>
+          <t>설정계약으로</t>
+        </is>
+      </c>
+      <c r="B219" s="8" t="n"/>
+      <c r="C219" s="8" t="n"/>
+      <c r="D219" s="8" t="n"/>
+      <c r="E219" s="8" t="n"/>
+      <c r="F219" s="8" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B220" s="8" t="n"/>
+      <c r="C220" s="8" t="n"/>
+      <c r="D220" s="8" t="n"/>
+      <c r="E220" s="8" t="n"/>
+      <c r="F220" s="8" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="7" t="inlineStr">
+        <is>
+          <t>2024년04월04일</t>
+        </is>
+      </c>
+      <c r="B221" s="8" t="n"/>
+      <c r="C221" s="8" t="n"/>
+      <c r="D221" s="8" t="n"/>
+      <c r="E221" s="8" t="n"/>
+      <c r="F221" s="8" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t>제29644호</t>
+        </is>
+      </c>
+      <c r="B222" s="8" t="n"/>
+      <c r="C222" s="8" t="n"/>
+      <c r="D222" s="8" t="n"/>
+      <c r="E222" s="8" t="n"/>
+      <c r="F222" s="8" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="7" t="inlineStr">
+        <is>
+          <t>설정계약으로</t>
+        </is>
+      </c>
+      <c r="B223" s="8" t="n"/>
+      <c r="C223" s="8" t="n"/>
+      <c r="D223" s="8" t="n"/>
+      <c r="E223" s="8" t="n"/>
+      <c r="F223" s="8" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B224" s="8" t="n"/>
+      <c r="C224" s="8" t="n"/>
+      <c r="D224" s="8" t="n"/>
+      <c r="E224" s="8" t="n"/>
+      <c r="F224" s="8" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="7" t="inlineStr">
+        <is>
+          <t>2024년04월04일</t>
+        </is>
+      </c>
+      <c r="B225" s="8" t="n"/>
+      <c r="C225" s="8" t="n"/>
+      <c r="D225" s="8" t="n"/>
+      <c r="E225" s="8" t="n"/>
+      <c r="F225" s="8" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="7" t="inlineStr">
+        <is>
+          <t>제29644호</t>
+        </is>
+      </c>
+      <c r="B226" s="8" t="n"/>
+      <c r="C226" s="8" t="n"/>
+      <c r="D226" s="8" t="n"/>
+      <c r="E226" s="8" t="n"/>
+      <c r="F226" s="8" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t>설정계약으로</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="n"/>
+      <c r="C227" s="8" t="n"/>
+      <c r="D227" s="8" t="n"/>
+      <c r="E227" s="8" t="n"/>
+      <c r="F227" s="8" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B228" s="8" t="n"/>
+      <c r="C228" s="8" t="n"/>
+      <c r="D228" s="8" t="n"/>
+      <c r="E228" s="8" t="n"/>
+      <c r="F228" s="8" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="7" t="inlineStr">
+        <is>
+          <t>11[토지]경기도파주시파평면마산리 ， 의정부지2024년04월04일</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="n"/>
+      <c r="C229" s="8" t="n"/>
+      <c r="D229" s="8" t="n"/>
+      <c r="E229" s="8" t="n"/>
+      <c r="F229" s="8" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="7" t="inlineStr">
+        <is>
+          <t>108-3고양지원제29644호</t>
+        </is>
+      </c>
+      <c r="B230" s="8" t="n"/>
+      <c r="C230" s="8" t="n"/>
+      <c r="D230" s="8" t="n"/>
+      <c r="E230" s="8" t="n"/>
+      <c r="F230" s="8" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="7" t="inlineStr">
+        <is>
+          <t>파주능기설정계약으로</t>
+        </is>
+      </c>
+      <c r="B231" s="8" t="n"/>
+      <c r="C231" s="8" t="n"/>
+      <c r="D231" s="8" t="n"/>
+      <c r="E231" s="8" t="n"/>
+      <c r="F231" s="8" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B232" s="8" t="n"/>
+      <c r="C232" s="8" t="n"/>
+      <c r="D232" s="8" t="n"/>
+      <c r="E232" s="8" t="n"/>
+      <c r="F232" s="8" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t>12[토지]경기도파주시파평면마산리 ， 의정부지방법2024년04월04일</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="n"/>
+      <c r="C233" s="8" t="n"/>
+      <c r="D233" s="8" t="n"/>
+      <c r="E233" s="8" t="n"/>
+      <c r="F233" s="8" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="7" t="inlineStr">
+        <is>
+          <t>108-4고양지원제29644호</t>
+        </is>
+      </c>
+      <c r="B234" s="8" t="n"/>
+      <c r="C234" s="8" t="n"/>
+      <c r="D234" s="8" t="n"/>
+      <c r="E234" s="8" t="n"/>
+      <c r="F234" s="8" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="7" t="inlineStr">
+        <is>
+          <t>파주능기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B235" s="8" t="n"/>
+      <c r="C235" s="8" t="n"/>
+      <c r="D235" s="8" t="n"/>
+      <c r="E235" s="8" t="n"/>
+      <c r="F235" s="8" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B236" s="8" t="n"/>
+      <c r="C236" s="8" t="n"/>
+      <c r="D236" s="8" t="n"/>
+      <c r="E236" s="8" t="n"/>
+      <c r="F236" s="8" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="7" t="inlineStr">
+        <is>
+          <t>열람일시 : 2026년03월31일17시25분59초</t>
+        </is>
+      </c>
+      <c r="B237" s="8" t="n"/>
+      <c r="C237" s="8" t="n"/>
+      <c r="D237" s="8" t="n"/>
+      <c r="E237" s="8" t="n"/>
+      <c r="F237" s="8" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="7" t="inlineStr">
+        <is>
+          <t>기타사항</t>
+        </is>
+      </c>
+      <c r="B238" s="8" t="n"/>
+      <c r="C238" s="8" t="n"/>
+      <c r="D238" s="8" t="n"/>
+      <c r="E238" s="8" t="n"/>
+      <c r="F238" s="8" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="7" t="inlineStr">
+        <is>
+          <t>생성원인변경 / 소멸</t>
+        </is>
+      </c>
+      <c r="B239" s="8" t="n"/>
+      <c r="C239" s="8" t="n"/>
+      <c r="D239" s="8" t="n"/>
+      <c r="E239" s="8" t="n"/>
+      <c r="F239" s="8" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="7" t="inlineStr">
+        <is>
+          <t>13[토지]경기도파주시파평면마산리 ， 의정부지방법원42024년04월04일</t>
+        </is>
+      </c>
+      <c r="B240" s="8" t="n"/>
+      <c r="C240" s="8" t="n"/>
+      <c r="D240" s="8" t="n"/>
+      <c r="E240" s="8" t="n"/>
+      <c r="F240" s="8" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="7" t="inlineStr">
+        <is>
+          <t>109-3고양지원제39644호</t>
+        </is>
+      </c>
+      <c r="B241" s="8" t="n"/>
+      <c r="C241" s="8" t="n"/>
+      <c r="D241" s="8" t="n"/>
+      <c r="E241" s="8" t="n"/>
+      <c r="F241" s="8" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="7" t="inlineStr">
+        <is>
+          <t>파주능기소설정계약으로</t>
+        </is>
+      </c>
+      <c r="B242" s="8" t="n"/>
+      <c r="C242" s="8" t="n"/>
+      <c r="D242" s="8" t="n"/>
+      <c r="E242" s="8" t="n"/>
+      <c r="F242" s="8" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B243" s="8" t="n"/>
+      <c r="C243" s="8" t="n"/>
+      <c r="D243" s="8" t="n"/>
+      <c r="E243" s="8" t="n"/>
+      <c r="F243" s="8" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="7" t="inlineStr">
+        <is>
+          <t>116-15고양지원제39644호</t>
+        </is>
+      </c>
+      <c r="B244" s="8" t="n"/>
+      <c r="C244" s="8" t="n"/>
+      <c r="D244" s="8" t="n"/>
+      <c r="E244" s="8" t="n"/>
+      <c r="F244" s="8" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="7" t="inlineStr">
+        <is>
+          <t>파주등기설정계약으로</t>
+        </is>
+      </c>
+      <c r="B245" s="8" t="n"/>
+      <c r="C245" s="8" t="n"/>
+      <c r="D245" s="8" t="n"/>
+      <c r="E245" s="8" t="n"/>
+      <c r="F245" s="8" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="7" t="inlineStr">
+        <is>
+          <t>인하여</t>
+        </is>
+      </c>
+      <c r="B246" s="8" t="n"/>
+      <c r="C246" s="8" t="n"/>
+      <c r="D246" s="8" t="n"/>
+      <c r="E246" s="8" t="n"/>
+      <c r="F246" s="8" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="7" t="inlineStr">
+        <is>
+          <t>기도파주시파평면마산리 | ， 의정부지2024년04월04일</t>
+        </is>
+      </c>
+      <c r="B247" s="8" t="n"/>
+      <c r="C247" s="8" t="n"/>
+      <c r="D247" s="8" t="n"/>
+      <c r="E247" s="8" t="n"/>
+      <c r="F247" s="8" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="7" t="inlineStr">
+        <is>
+          <t>산44-7고양지원제39644호</t>
+        </is>
+      </c>
+      <c r="B248" s="8" t="n"/>
+      <c r="C248" s="8" t="n"/>
+      <c r="D248" s="8" t="n"/>
+      <c r="E248" s="8" t="n"/>
+      <c r="F248" s="8" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="7" t="inlineStr">
+        <is>
+          <t>파주능기설정계약으로</t>
+        </is>
+      </c>
+      <c r="B249" s="8" t="n"/>
+      <c r="C249" s="8" t="n"/>
+      <c r="D249" s="8" t="n"/>
+      <c r="E249" s="8" t="n"/>
+      <c r="F249" s="8" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="7" t="inlineStr">
+        <is>
+          <t>지원파주능기소</t>
+        </is>
+      </c>
+      <c r="B250" s="8" t="n"/>
+      <c r="C250" s="8" t="n"/>
+      <c r="D250" s="8" t="n"/>
+      <c r="E250" s="8" t="n"/>
+      <c r="F250" s="8" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="7" t="inlineStr">
+        <is>
+          <t>* 실선으로그어진부분은말소사항을표시함 * 기록사항없는갑구 , 을구는 ' 기록사항없음 ' 으로표시함 .</t>
+        </is>
+      </c>
+      <c r="B251" s="8" t="n"/>
+      <c r="C251" s="8" t="n"/>
+      <c r="D251" s="8" t="n"/>
+      <c r="E251" s="8" t="n"/>
+      <c r="F251" s="8" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="7" t="inlineStr">
+        <is>
+          <t>* 증명서는컬러또는흑백으로출력가능함 .</t>
+        </is>
+      </c>
+      <c r="B252" s="8" t="n"/>
+      <c r="C252" s="8" t="n"/>
+      <c r="D252" s="8" t="n"/>
+      <c r="E252" s="8" t="n"/>
+      <c r="F252" s="8" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="7" t="inlineStr">
+        <is>
+          <t>* 본능기사항중명서는열람용이므로출력하신능기사항중명서는법적인효력이없습니다 .</t>
+        </is>
+      </c>
+      <c r="B253" s="8" t="n"/>
+      <c r="C253" s="8" t="n"/>
+      <c r="D253" s="8" t="n"/>
+      <c r="E253" s="8" t="n"/>
+      <c r="F253" s="8" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="7" t="inlineStr">
+        <is>
+          <t>열람일시 : 2026년03월31일17시25분59초</t>
+        </is>
+      </c>
+      <c r="B254" s="8" t="n"/>
+      <c r="C254" s="8" t="n"/>
+      <c r="D254" s="8" t="n"/>
+      <c r="E254" s="8" t="n"/>
+      <c r="F254" s="8" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="7" t="inlineStr">
+        <is>
+          <t>주요등기사항요약(참고용)</t>
+        </is>
+      </c>
+      <c r="B255" s="8" t="n"/>
+      <c r="C255" s="8" t="n"/>
+      <c r="D255" s="8" t="n"/>
+      <c r="E255" s="8" t="n"/>
+      <c r="F255" s="8" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="7" t="inlineStr">
+        <is>
+          <t>떠 Ho</t>
+        </is>
+      </c>
+      <c r="B256" s="8" t="n"/>
+      <c r="C256" s="8" t="n"/>
+      <c r="D256" s="8" t="n"/>
+      <c r="E256" s="8" t="n"/>
+      <c r="F256" s="8" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="7" t="inlineStr">
+        <is>
+          <t>래누</t>
+        </is>
+      </c>
+      <c r="B257" s="8" t="n"/>
+      <c r="C257" s="8" t="n"/>
+      <c r="D257" s="8" t="n"/>
+      <c r="E257" s="8" t="n"/>
+      <c r="F257" s="8" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="7" t="inlineStr">
+        <is>
+          <t>태하</t>
+        </is>
+      </c>
+      <c r="B258" s="8" t="n"/>
+      <c r="C258" s="8" t="n"/>
+      <c r="D258" s="8" t="n"/>
+      <c r="E258" s="8" t="n"/>
+      <c r="F258" s="8" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="7" t="inlineStr">
+        <is>
+          <t>ae: 홀</t>
+        </is>
+      </c>
+      <c r="B259" s="8" t="n"/>
+      <c r="C259" s="8" t="n"/>
+      <c r="D259" s="8" t="n"/>
+      <c r="E259" s="8" t="n"/>
+      <c r="F259" s="8" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="7" t="inlineStr">
+        <is>
+          <t>10디 oO</t>
+        </is>
+      </c>
+      <c r="B260" s="8" t="n"/>
+      <c r="C260" s="8" t="n"/>
+      <c r="D260" s="8" t="n"/>
+      <c r="E260" s="8" t="n"/>
+      <c r="F260" s="8" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="7" t="inlineStr">
+        <is>
+          <t>~ pm 발</t>
+        </is>
+      </c>
+      <c r="B261" s="8" t="n"/>
+      <c r="C261" s="8" t="n"/>
+      <c r="D261" s="8" t="n"/>
+      <c r="E261" s="8" t="n"/>
+      <c r="F261" s="8" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="7" t="inlineStr">
+        <is>
+          <t>대 q]문매숙</t>
+        </is>
+      </c>
+      <c r="B262" s="8" t="n"/>
+      <c r="C262" s="8" t="n"/>
+      <c r="D262" s="8" t="n"/>
+      <c r="E262" s="8" t="n"/>
+      <c r="F262" s="8" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="7" t="inlineStr">
+        <is>
+          <t>~ jou jou . 그 ol!</t>
+        </is>
+      </c>
+      <c r="B263" s="8" t="n"/>
+      <c r="C263" s="8" t="n"/>
+      <c r="D263" s="8" t="n"/>
+      <c r="E263" s="8" t="n"/>
+      <c r="F263" s="8" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="7">
+        <f>» nd ad | aM 급 \</f>
+        <v/>
+      </c>
+      <c r="B264" s="8" t="n"/>
+      <c r="C264" s="8" t="n"/>
+      <c r="D264" s="8" t="n"/>
+      <c r="E264" s="8" t="n"/>
+      <c r="F264" s="8" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="7" t="inlineStr">
+        <is>
+          <t>110 一 야2비 ㅜ ob aril</t>
+        </is>
+      </c>
+      <c r="B265" s="8" t="n"/>
+      <c r="C265" s="8" t="n"/>
+      <c r="D265" s="8" t="n"/>
+      <c r="E265" s="8" t="n"/>
+      <c r="F265" s="8" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="7" t="inlineStr">
+        <is>
+          <t>ou o Ho | Sito oF 근 x ~</t>
+        </is>
+      </c>
+      <c r="B266" s="8" t="n"/>
+      <c r="C266" s="8" t="n"/>
+      <c r="D266" s="8" t="n"/>
+      <c r="E266" s="8" t="n"/>
+      <c r="F266" s="8" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="7" t="inlineStr">
+        <is>
+          <t>겪 x Se | Spm S ee . 가</t>
+        </is>
+      </c>
+      <c r="B267" s="8" t="n"/>
+      <c r="C267" s="8" t="n"/>
+      <c r="D267" s="8" t="n"/>
+      <c r="E267" s="8" t="n"/>
+      <c r="F267" s="8" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="7" t="inlineStr">
+        <is>
+          <t>ㅇ ^ ~ 으 《 Ke 규</t>
+        </is>
+      </c>
+      <c r="B268" s="8" t="n"/>
+      <c r="C268" s="8" t="n"/>
+      <c r="D268" s="8" t="n"/>
+      <c r="E268" s="8" t="n"/>
+      <c r="F268" s="8" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="7" t="inlineStr">
+        <is>
+          <t>3 ” | 음어애 et 으며는 .</t>
+        </is>
+      </c>
+      <c r="B269" s="8" t="n"/>
+      <c r="C269" s="8" t="n"/>
+      <c r="D269" s="8" t="n"/>
+      <c r="E269" s="8" t="n"/>
+      <c r="F269" s="8" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="7" t="inlineStr">
+        <is>
+          <t>다사、」 S4 © io = jo”</t>
+        </is>
+      </c>
+      <c r="B270" s="8" t="n"/>
+      <c r="C270" s="8" t="n"/>
+      <c r="D270" s="8" t="n"/>
+      <c r="E270" s="8" t="n"/>
+      <c r="F270" s="8" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="7" t="inlineStr">
+        <is>
+          <t>中 묵 nh dH NE ONE “和 叫 olf! pr</t>
+        </is>
+      </c>
+      <c r="B271" s="8" t="n"/>
+      <c r="C271" s="8" t="n"/>
+      <c r="D271" s="8" t="n"/>
+      <c r="E271" s="8" t="n"/>
+      <c r="F271" s="8" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="7" t="inlineStr">
+        <is>
+          <t>ac Sg | Sa 퍼 | ow a x</t>
+        </is>
+      </c>
+      <c r="B272" s="8" t="n"/>
+      <c r="C272" s="8" t="n"/>
+      <c r="D272" s="8" t="n"/>
+      <c r="E272" s="8" t="n"/>
+      <c r="F272" s="8" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="7" t="inlineStr">
+        <is>
+          <t>여돈 &lt; Moar | rear ° OK</t>
+        </is>
+      </c>
+      <c r="B273" s="8" t="n"/>
+      <c r="C273" s="8" t="n"/>
+      <c r="D273" s="8" t="n"/>
+      <c r="E273" s="8" t="n"/>
+      <c r="F273" s="8" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="7" t="inlineStr">
+        <is>
+          <t>꼬12 、 고으</t>
+        </is>
+      </c>
+      <c r="B274" s="8" t="n"/>
+      <c r="C274" s="8" t="n"/>
+      <c r="D274" s="8" t="n"/>
+      <c r="E274" s="8" t="n"/>
+      <c r="F274" s="8" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="7" t="inlineStr">
+        <is>
+          <t>jo , a 습농 oO</t>
+        </is>
+      </c>
+      <c r="B275" s="8" t="n"/>
+      <c r="C275" s="8" t="n"/>
+      <c r="D275" s="8" t="n"/>
+      <c r="E275" s="8" t="n"/>
+      <c r="F275" s="8" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="7" t="inlineStr">
+        <is>
+          <t>ar 스 aK | OK arc + il 家 ay</t>
+        </is>
+      </c>
+      <c r="B276" s="8" t="n"/>
+      <c r="C276" s="8" t="n"/>
+      <c r="D276" s="8" t="n"/>
+      <c r="E276" s="8" t="n"/>
+      <c r="F276" s="8" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="7" t="inlineStr">
+        <is>
+          <t>NS ' 녀 | 디 ana 죠패 oy 로</t>
+        </is>
+      </c>
+      <c r="B277" s="8" t="n"/>
+      <c r="C277" s="8" t="n"/>
+      <c r="D277" s="8" t="n"/>
+      <c r="E277" s="8" t="n"/>
+      <c r="F277" s="8" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="7" t="inlineStr">
+        <is>
+          <t>of ‘od 르넥당 NG TO 810 on 人 之</t>
+        </is>
+      </c>
+      <c r="B278" s="8" t="n"/>
+      <c r="C278" s="8" t="n"/>
+      <c r="D278" s="8" t="n"/>
+      <c r="E278" s="8" t="n"/>
+      <c r="F278" s="8" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="7" t="inlineStr">
+        <is>
+          <t>× 는2 全 x m PI! = ‘Oy ww</t>
+        </is>
+      </c>
+      <c r="B279" s="8" t="n"/>
+      <c r="C279" s="8" t="n"/>
+      <c r="D279" s="8" t="n"/>
+      <c r="E279" s="8" t="n"/>
+      <c r="F279" s="8" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="7" t="inlineStr">
+        <is>
+          <t>oy 部 응 \ 0 * eae</t>
+        </is>
+      </c>
+      <c r="B280" s="8" t="n"/>
+      <c r="C280" s="8" t="n"/>
+      <c r="D280" s="8" t="n"/>
+      <c r="E280" s="8" t="n"/>
+      <c r="F280" s="8" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="7" t="inlineStr">
+        <is>
+          <t>of oF 패 nu 0 nye | 9 中 5 中</t>
+        </is>
+      </c>
+      <c r="B281" s="8" t="n"/>
+      <c r="C281" s="8" t="n"/>
+      <c r="D281" s="8" t="n"/>
+      <c r="E281" s="8" t="n"/>
+      <c r="F281" s="8" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="7" t="inlineStr">
+        <is>
+          <t>人 0 K Ft! 6 = 리 = Ho 동 yo 때</t>
+        </is>
+      </c>
+      <c r="B282" s="8" t="n"/>
+      <c r="C282" s="8" t="n"/>
+      <c r="D282" s="8" t="n"/>
+      <c r="E282" s="8" t="n"/>
+      <c r="F282" s="8" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="7" t="inlineStr">
+        <is>
+          <t>KX p Mo ~ 디없 a io | 이 | 8예</t>
+        </is>
+      </c>
+      <c r="B283" s="8" t="n"/>
+      <c r="C283" s="8" t="n"/>
+      <c r="D283" s="8" t="n"/>
+      <c r="E283" s="8" t="n"/>
+      <c r="F283" s="8" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="7" t="inlineStr">
+        <is>
+          <t>當 Be 2 .에0껄8 No | ㅇ 02끓뺀인 . of)a</t>
+        </is>
+      </c>
+      <c r="B284" s="8" t="n"/>
+      <c r="C284" s="8" t="n"/>
+      <c r="D284" s="8" t="n"/>
+      <c r="E284" s="8" t="n"/>
+      <c r="F284" s="8" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="7" t="inlineStr">
+        <is>
+          <t>써 Me = ral oS mS | S | me 에픈패문</t>
+        </is>
+      </c>
+      <c r="B285" s="8" t="n"/>
+      <c r="C285" s="8" t="n"/>
+      <c r="D285" s="8" t="n"/>
+      <c r="E285" s="8" t="n"/>
+      <c r="F285" s="8" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="7" t="inlineStr">
+        <is>
+          <t>패 “ 럼운국의 | 해으 | 클이눈우제우</t>
+        </is>
+      </c>
+      <c r="B286" s="8" t="n"/>
+      <c r="C286" s="8" t="n"/>
+      <c r="D286" s="8" t="n"/>
+      <c r="E286" s="8" t="n"/>
+      <c r="F286" s="8" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="7" t="inlineStr">
+        <is>
+          <t>__ 뭐구스구 NK ~ 스눈 No N 더 x ah 비</t>
+        </is>
+      </c>
+      <c r="B287" s="8" t="n"/>
+      <c r="C287" s="8" t="n"/>
+      <c r="D287" s="8" t="n"/>
+      <c r="E287" s="8" t="n"/>
+      <c r="F287" s="8" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="7" t="inlineStr">
+        <is>
+          <t>조 eal Hol i RX | RK | aE oF 는의께</t>
+        </is>
+      </c>
+      <c r="B288" s="8" t="n"/>
+      <c r="C288" s="8" t="n"/>
+      <c r="D288" s="8" t="n"/>
+      <c r="E288" s="8" t="n"/>
+      <c r="F288" s="8" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="7" t="inlineStr">
+        <is>
+          <t>wm nr 계90짜 ob</t>
+        </is>
+      </c>
+      <c r="B289" s="8" t="n"/>
+      <c r="C289" s="8" t="n"/>
+      <c r="D289" s="8" t="n"/>
+      <c r="E289" s="8" t="n"/>
+      <c r="F289" s="8" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="7" t="inlineStr">
+        <is>
+          <t>x lo 깝 xo ~ Ko dd Fe</t>
+        </is>
+      </c>
+      <c r="B290" s="8" t="n"/>
+      <c r="C290" s="8" t="n"/>
+      <c r="D290" s="8" t="n"/>
+      <c r="E290" s="8" t="n"/>
+      <c r="F290" s="8" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="7" t="inlineStr">
+        <is>
+          <t>10스 Fe x Ke</t>
+        </is>
+      </c>
+      <c r="B291" s="8" t="n"/>
+      <c r="C291" s="8" t="n"/>
+      <c r="D291" s="8" t="n"/>
+      <c r="E291" s="8" t="n"/>
+      <c r="F291" s="8" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="7" t="inlineStr">
+        <is>
+          <t>그 ~ | 스 of 字 ulo ob 이이</t>
+        </is>
+      </c>
+      <c r="B292" s="8" t="n"/>
+      <c r="C292" s="8" t="n"/>
+      <c r="D292" s="8" t="n"/>
+      <c r="E292" s="8" t="n"/>
+      <c r="F292" s="8" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="7" t="inlineStr">
+        <is>
+          <t>2 一 NE x 깥패는 , 3</t>
+        </is>
+      </c>
+      <c r="B293" s="8" t="n"/>
+      <c r="C293" s="8" t="n"/>
+      <c r="D293" s="8" t="n"/>
+      <c r="E293" s="8" t="n"/>
+      <c r="F293" s="8" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="7" t="inlineStr">
+        <is>
+          <t>ag 에이는 ew RIS | &amp; Code</t>
+        </is>
+      </c>
+      <c r="B294" s="8" t="n"/>
+      <c r="C294" s="8" t="n"/>
+      <c r="D294" s="8" t="n"/>
+      <c r="E294" s="8" t="n"/>
+      <c r="F294" s="8" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="7" t="inlineStr">
+        <is>
+          <t>ㅇ w 급 &gt; 70 &lt; 능</t>
+        </is>
+      </c>
+      <c r="B295" s="8" t="n"/>
+      <c r="C295" s="8" t="n"/>
+      <c r="D295" s="8" t="n"/>
+      <c r="E295" s="8" t="n"/>
+      <c r="F295" s="8" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="7" t="inlineStr">
+        <is>
+          <t>全 密 너0히 BK o NO FO</t>
+        </is>
+      </c>
+      <c r="B296" s="8" t="n"/>
+      <c r="C296" s="8" t="n"/>
+      <c r="D296" s="8" t="n"/>
+      <c r="E296" s="8" t="n"/>
+      <c r="F296" s="8" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="7" t="inlineStr">
+        <is>
+          <t>트도 ㅡ 000 | 9이 vaya blo TF</t>
+        </is>
+      </c>
+      <c r="B297" s="8" t="n"/>
+      <c r="C297" s="8" t="n"/>
+      <c r="D297" s="8" t="n"/>
+      <c r="E297" s="8" t="n"/>
+      <c r="F297" s="8" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="7" t="inlineStr">
+        <is>
+          <t>blo X ~ ooh)oO 빌 \ &lt; 스</t>
+        </is>
+      </c>
+      <c r="B298" s="8" t="n"/>
+      <c r="C298" s="8" t="n"/>
+      <c r="D298" s="8" t="n"/>
+      <c r="E298" s="8" t="n"/>
+      <c r="F298" s="8" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="7" t="inlineStr">
+        <is>
+          <t>He} oe ele | o | 준께 —e ane</t>
+        </is>
+      </c>
+      <c r="B299" s="8" t="n"/>
+      <c r="C299" s="8" t="n"/>
+      <c r="D299" s="8" t="n"/>
+      <c r="E299" s="8" t="n"/>
+      <c r="F299" s="8" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="7" t="inlineStr">
+        <is>
+          <t>KE 레 一 說 i mm joo THT 때 Me op</t>
+        </is>
+      </c>
+      <c r="B300" s="8" t="n"/>
+      <c r="C300" s="8" t="n"/>
+      <c r="D300" s="8" t="n"/>
+      <c r="E300" s="8" t="n"/>
+      <c r="F300" s="8" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="7">
+        <f> = | ue ㄷ . RYO 선</f>
+        <v/>
+      </c>
+      <c r="B301" s="8" t="n"/>
+      <c r="C301" s="8" t="n"/>
+      <c r="D301" s="8" t="n"/>
+      <c r="E301" s="8" t="n"/>
+      <c r="F301" s="8" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="7" t="inlineStr">
+        <is>
+          <t>쩌)3 my 써1 ~ No ak! &lt;0</t>
+        </is>
+      </c>
+      <c r="B302" s="8" t="n"/>
+      <c r="C302" s="8" t="n"/>
+      <c r="D302" s="8" t="n"/>
+      <c r="E302" s="8" t="n"/>
+      <c r="F302" s="8" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="7" t="inlineStr">
+        <is>
+          <t>그음 . ~ rule me KF</t>
+        </is>
+      </c>
+      <c r="B303" s="8" t="n"/>
+      <c r="C303" s="8" t="n"/>
+      <c r="D303" s="8" t="n"/>
+      <c r="E303" s="8" t="n"/>
+      <c r="F303" s="8" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="7" t="inlineStr">
+        <is>
+          <t>: 202643월319오후5시25분59초</t>
+        </is>
+      </c>
+      <c r="B304" s="8" t="n"/>
+      <c r="C304" s="8" t="n"/>
+      <c r="D304" s="8" t="n"/>
+      <c r="E304" s="8" t="n"/>
+      <c r="F304" s="8" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="7" t="inlineStr">
+        <is>
+          <t>출력일시</t>
+        </is>
+      </c>
+      <c r="B305" s="8" t="n"/>
+      <c r="C305" s="8" t="n"/>
+      <c r="D305" s="8" t="n"/>
+      <c r="E305" s="8" t="n"/>
+      <c r="F305" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="302">
+    <mergeCell ref="A174:F174"/>
+    <mergeCell ref="A205:F205"/>
+    <mergeCell ref="A183:F183"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A118:F118"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A133:F133"/>
+    <mergeCell ref="A189:F189"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A198:F198"/>
+    <mergeCell ref="A238:F238"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A239:F239"/>
+    <mergeCell ref="A301:F301"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="A175:F175"/>
+    <mergeCell ref="A150:F150"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A263:F263"/>
+    <mergeCell ref="A144:F144"/>
+    <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A303:F303"/>
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A290:F290"/>
+    <mergeCell ref="A224:F224"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A134:F134"/>
+    <mergeCell ref="A200:F200"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A152:F152"/>
+    <mergeCell ref="A265:F265"/>
+    <mergeCell ref="A121:F121"/>
+    <mergeCell ref="A280:F280"/>
+    <mergeCell ref="A161:F161"/>
+    <mergeCell ref="A274:F274"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A288:F288"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A249:F249"/>
+    <mergeCell ref="A289:F289"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A202:F202"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A258:F258"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A186:F186"/>
+    <mergeCell ref="A257:F257"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A107:F107"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A226:F226"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A260:F260"/>
+    <mergeCell ref="A266:F266"/>
+    <mergeCell ref="A291:F291"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A241:F241"/>
+    <mergeCell ref="A250:F250"/>
+    <mergeCell ref="A228:F228"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A237:F237"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A172:F172"/>
+    <mergeCell ref="A212:F212"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A221:F221"/>
+    <mergeCell ref="A243:F243"/>
+    <mergeCell ref="A252:F252"/>
+    <mergeCell ref="A108:F108"/>
+    <mergeCell ref="A277:F277"/>
+    <mergeCell ref="A283:F283"/>
+    <mergeCell ref="A286:F286"/>
+    <mergeCell ref="A292:F292"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A236:F236"/>
+    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A214:F214"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A163:F163"/>
+    <mergeCell ref="A267:F267"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A223:F223"/>
+    <mergeCell ref="A285:F285"/>
+    <mergeCell ref="A294:F294"/>
+    <mergeCell ref="A195:F195"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A204:F204"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A213:F213"/>
+    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="A269:F269"/>
+    <mergeCell ref="A278:F278"/>
+    <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A141:F141"/>
+    <mergeCell ref="A254:F254"/>
+    <mergeCell ref="A259:F259"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A206:F206"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A240:F240"/>
+    <mergeCell ref="A122:F122"/>
+    <mergeCell ref="A215:F215"/>
+    <mergeCell ref="A262:F262"/>
+    <mergeCell ref="A125:F125"/>
+    <mergeCell ref="A190:F190"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A112:F112"/>
+    <mergeCell ref="A199:F199"/>
+    <mergeCell ref="A230:F230"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A127:F127"/>
+    <mergeCell ref="A167:F167"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A176:F176"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A114:F114"/>
+    <mergeCell ref="A232:F232"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A142:F142"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A182:F182"/>
+    <mergeCell ref="A304:F304"/>
+    <mergeCell ref="A216:F216"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A191:F191"/>
+    <mergeCell ref="A169:F169"/>
+    <mergeCell ref="A225:F225"/>
+    <mergeCell ref="A296:F296"/>
+    <mergeCell ref="A178:F178"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A153:F153"/>
+    <mergeCell ref="A162:F162"/>
+    <mergeCell ref="A218:F218"/>
+    <mergeCell ref="A227:F227"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A137:F137"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A177:F177"/>
+    <mergeCell ref="A208:F208"/>
+    <mergeCell ref="A217:F217"/>
+    <mergeCell ref="A268:F268"/>
+    <mergeCell ref="A164:F164"/>
+    <mergeCell ref="A282:F282"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A105:F105"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A145:F145"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A139:F139"/>
+    <mergeCell ref="A154:F154"/>
+    <mergeCell ref="A210:F210"/>
+    <mergeCell ref="A179:F179"/>
+    <mergeCell ref="A272:F272"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A129:F129"/>
+    <mergeCell ref="A242:F242"/>
+    <mergeCell ref="A251:F251"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A203:F203"/>
+    <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A181:F181"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A131:F131"/>
+    <mergeCell ref="A196:F196"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A244:F244"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A165:F165"/>
+    <mergeCell ref="A171:F171"/>
+    <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A231:F231"/>
+    <mergeCell ref="A253:F253"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A299:F299"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A293:F293"/>
+    <mergeCell ref="A93:F93"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A173:F173"/>
+    <mergeCell ref="A229:F229"/>
+    <mergeCell ref="A111:F111"/>
+    <mergeCell ref="A295:F295"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A143:F143"/>
+    <mergeCell ref="A245:F245"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A157:F157"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A270:F270"/>
+    <mergeCell ref="A276:F276"/>
+    <mergeCell ref="A166:F166"/>
+    <mergeCell ref="A279:F279"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A207:F207"/>
+    <mergeCell ref="A300:F300"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A287:F287"/>
+    <mergeCell ref="A168:F168"/>
+    <mergeCell ref="A281:F281"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A256:F256"/>
+    <mergeCell ref="A271:F271"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A246:F246"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A193:F193"/>
+    <mergeCell ref="A255:F255"/>
+    <mergeCell ref="A264:F264"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A233:F233"/>
+    <mergeCell ref="A273:F273"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A120:F120"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A192:F192"/>
+    <mergeCell ref="A248:F248"/>
+    <mergeCell ref="A104:F104"/>
+    <mergeCell ref="A297:F297"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A235:F235"/>
+    <mergeCell ref="A302:F302"/>
+    <mergeCell ref="A247:F247"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A185:F185"/>
+    <mergeCell ref="A298:F298"/>
+    <mergeCell ref="A219:F219"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A194:F194"/>
+    <mergeCell ref="A106:F106"/>
+    <mergeCell ref="A234:F234"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A147:F147"/>
+    <mergeCell ref="A184:F184"/>
+    <mergeCell ref="A209:F209"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A156:F156"/>
+    <mergeCell ref="A170:F170"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A155:F155"/>
+    <mergeCell ref="A211:F211"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A220:F220"/>
+    <mergeCell ref="A305:F305"/>
+    <mergeCell ref="A130:F130"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A201:F201"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="A261:F261"/>
+    <mergeCell ref="A275:F275"/>
+    <mergeCell ref="A284:F284"/>
+    <mergeCell ref="A222:F222"/>
     <mergeCell ref="B1:H1"/>
+    <mergeCell ref="A123:F123"/>
+    <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A132:F132"/>
+    <mergeCell ref="A197:F197"/>
+    <mergeCell ref="A110:F110"/>
+    <mergeCell ref="A146:F146"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A119:F119"/>
+    <mergeCell ref="A187:F187"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -716,7 +5745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -734,35 +5763,407 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>순위번호</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>등기목적</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>권리자</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>금액/지분</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>순위번호 | 등기목적접수동기원인권리자및기타사항</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>말소제10277호해지</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>9근저당권설정2024년02월14일 ， 2024년02월14일채권최고액금221,000,000원</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>제10278호설정계약 AEX 이순옥</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시문산읍사임당로65-30</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>근저당권자북파주농업협동조합</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>115636-0000297</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시문산읍문향로75</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>(파평지점)</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>공동담보목록제2024-225호</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>10근저당권설정2024년02월14일2024년02월14일채권최고액금130,000,000원</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>제10279호설정계약 AEX 이순옥</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시문산읍사임당로65-30</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>근저당권자북파주농업협동조합</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>115636-0000297</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시문산읍문향로75</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>(파평지점)</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>〈_꽤 - ㅠ 7} oS Al]2024-2268.</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>11지상권설정2024톨떨촬욜일20241큭′휠_모끓끝</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>제10280호 ㅋ Ag 73 APE</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2024144849)</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>제29644호</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>열람일시 : 2026년03월31일17시25분59초</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>2024년04월04일</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>설정계약</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>채권최고액금360,000,000원</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>채무자강성원</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>경기도파주시문산읍사임당로65-30</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>서울특별시마포구마포대로4라길30,106농</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>802호(마포농 , 마포쌍용황금아파트)</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>공동담보목록제2024-558호</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="32">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B1:F1"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -792,27 +6193,27 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>순위번호</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>등기목적</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>권리자</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>금액/지분</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
